--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -1,149 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\phd\05_multi_performative_stable\multiplayer-performative-stable\multi_regression\figs_100\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32BD2FA-6942-480D-ACBD-07B16E9BCC43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>$\sigma_A$ = 0.25</t>
-  </si>
-  <si>
-    <t>$\sigma_A$ = 0.5</t>
-  </si>
-  <si>
-    <t>$\sigma_A$ = 0.75</t>
-  </si>
-  <si>
-    <t>$\sigma_A$ = 1.0</t>
-  </si>
-  <si>
-    <t>RR</t>
-  </si>
-  <si>
-    <t>0.0041 $\pm$ 0.0004</t>
-  </si>
-  <si>
-    <t>0.0045 $\pm$ 0.0003</t>
-  </si>
-  <si>
-    <t>0.0047 $\pm$ 0.0004</t>
-  </si>
-  <si>
-    <t>0.0048 $\pm$ 0.0004</t>
-  </si>
-  <si>
-    <t>RGD</t>
-  </si>
-  <si>
-    <t>0.0050 $\pm$ 0.0004</t>
-  </si>
-  <si>
-    <t>0.0467 $\pm$ 0.1248</t>
-  </si>
-  <si>
-    <t>0.0472 $\pm$ 0.1253</t>
-  </si>
-  <si>
-    <t>0.0514 $\pm$ 0.1364</t>
-  </si>
-  <si>
-    <t>SFB</t>
-  </si>
-  <si>
-    <t>0.2627 $\pm$ 0.0705</t>
-  </si>
-  <si>
-    <t>0.2451 $\pm$ 0.1816</t>
-  </si>
-  <si>
-    <t>0.2638 $\pm$ 0.2655</t>
-  </si>
-  <si>
-    <t>0.2948 $\pm$ 0.3774</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>0.1679 $\pm$ 0.0647</t>
-  </si>
-  <si>
-    <t>0.1823 $\pm$ 0.0984</t>
-  </si>
-  <si>
-    <t>0.2087 $\pm$ 0.1347</t>
-  </si>
-  <si>
-    <t>0.2343 $\pm$ 0.1659</t>
-  </si>
-  <si>
-    <t>OPGD</t>
-  </si>
-  <si>
-    <t>0.0453 $\pm$ 0.0239</t>
-  </si>
-  <si>
-    <t>0.0368 $\pm$ 0.0138</t>
-  </si>
-  <si>
-    <t>0.0300 $\pm$ 0.0135</t>
-  </si>
-  <si>
-    <t>0.0231 $\pm$ 0.0120</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -152,93 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -526,115 +420,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="5" width="18.54296875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>$\sigma_A$ = 0.25</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>$\sigma_A$ = 0.5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>$\sigma_A$ = 0.75</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>$\sigma_A$ = 1.0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SIR$^2$</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.0041 $\pm$ 0.0004</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0045 $\pm$ 0.0003</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.0047 $\pm$ 0.0004</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0048 $\pm$ 0.0004</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RGD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.0050 $\pm$ 0.0004</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0467 $\pm$ 0.1248</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0472 $\pm$ 0.1253</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0514 $\pm$ 0.1364</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SFB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.2627 $\pm$ 0.0705</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.2451 $\pm$ 0.1816</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.2638 $\pm$ 0.2655</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.2948 $\pm$ 0.3774</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.1679 $\pm$ 0.0647</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.1823 $\pm$ 0.0984</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.2087 $\pm$ 0.1347</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.2343 $\pm$ 0.1659</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>28</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OPGD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.0453 $\pm$ 0.0239</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0368 $\pm$ 0.0138</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0300 $\pm$ 0.0135</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0231 $\pm$ 0.0120</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0041 $\pm$ 0.0004</t>
+          <t>0.0041 $\pm$ 0.0003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,130 +463,157 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0041 $\pm$ 0.0003</t>
+          <t>0.0043 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0045 $\pm$ 0.0003</t>
+          <t>0.0045 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0047 $\pm$ 0.0004</t>
+          <t>0.0044 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0048 $\pm$ 0.0004</t>
+          <t>0.0042 $\pm$ 0.0001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>RGD</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0050 $\pm$ 0.0004</t>
+          <t>0.0052 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0467 $\pm$ 0.1248</t>
+          <t>0.0052 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0472 $\pm$ 0.1253</t>
+          <t>0.0052 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0514 $\pm$ 0.1364</t>
+          <t>0.0052 $\pm$ 0.0002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SFB</t>
+          <t>RGD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2627 $\pm$ 0.0705</t>
+          <t>0.0052 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.2451 $\pm$ 0.1816</t>
+          <t>0.0054 $\pm$ 0.0007</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.2638 $\pm$ 0.2655</t>
+          <t>0.0054 $\pm$ 0.0006</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2948 $\pm$ 0.3774</t>
+          <t>0.0054 $\pm$ 0.0004</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>SFB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.1679 $\pm$ 0.0647</t>
+          <t>0.2615 $\pm$ 0.0724</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.1823 $\pm$ 0.0984</t>
+          <t>0.1948 $\pm$ 0.1472</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.2087 $\pm$ 0.1347</t>
+          <t>0.1601 $\pm$ 0.1217</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2343 $\pm$ 0.1659</t>
+          <t>0.1301 $\pm$ 0.0920</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.0050 $\pm$ 0.0002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0056 $\pm$ 0.0005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0055 $\pm$ 0.0003</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0053 $\pm$ 0.0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>OPGD</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.0453 $\pm$ 0.0239</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.0368 $\pm$ 0.0138</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.0300 $\pm$ 0.0135</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0231 $\pm$ 0.0120</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.0394 $\pm$ 0.0222</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.1041 $\pm$ 0.0500</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0930 $\pm$ 0.0429</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0739 $\pm$ 0.0338</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0043 $\pm$ 0.0002</t>
+          <t>0.0049 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0045 $\pm$ 0.0002</t>
+          <t>0.0049 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0044 $\pm$ 0.0002</t>
+          <t>0.0049 $\pm$ 0.0002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0042 $\pm$ 0.0001</t>
+          <t>0.0049 $\pm$ 0.0002</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0052 $\pm$ 0.0002</t>
+          <t>0.0387 $\pm$ 0.0081</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0054 $\pm$ 0.0007</t>
+          <t>0.0350 $\pm$ 0.0177</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0054 $\pm$ 0.0006</t>
+          <t>0.0349 $\pm$ 0.0144</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0054 $\pm$ 0.0004</t>
+          <t>0.0352 $\pm$ 0.0105</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2615 $\pm$ 0.0724</t>
+          <t>0.3812 $\pm$ 0.0908</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.1948 $\pm$ 0.1472</t>
+          <t>0.2561 $\pm$ 0.1878</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.1601 $\pm$ 0.1217</t>
+          <t>0.2067 $\pm$ 0.1416</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.1301 $\pm$ 0.0920</t>
+          <t>0.1671 $\pm$ 0.1010</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0050 $\pm$ 0.0002</t>
+          <t>0.0183 $\pm$ 0.0065</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0056 $\pm$ 0.0005</t>
+          <t>0.1078 $\pm$ 0.0751</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0055 $\pm$ 0.0003</t>
+          <t>0.0811 $\pm$ 0.0544</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0053 $\pm$ 0.0002</t>
+          <t>0.0616 $\pm$ 0.0288</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>$\sigma_A$ = 0.25</t>
+          <t>$\sigma_A$ = 10.0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>$\sigma_A$ = 0.5</t>
+          <t>$\sigma_A$ = 2.5</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>$\sigma_A$ = 0.75</t>
+          <t>$\sigma_A$ = 5.0</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>$\sigma_A$ = 1.0</t>
+          <t>$\sigma_A$ = 7.5</t>
         </is>
       </c>
     </row>
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0049 $\pm$ 0.0002</t>
+          <t>0.0272 $\pm$ 0.0021</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0049 $\pm$ 0.0002</t>
+          <t>0.0272 $\pm$ 0.0021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0049 $\pm$ 0.0002</t>
+          <t>0.0272 $\pm$ 0.0021</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0049 $\pm$ 0.0002</t>
+          <t>0.0272 $\pm$ 0.0021</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0052 $\pm$ 0.0002</t>
+          <t>0.1229 $\pm$ 0.0370</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0052 $\pm$ 0.0002</t>
+          <t>0.1022 $\pm$ 0.0713</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0052 $\pm$ 0.0002</t>
+          <t>0.1145 $\pm$ 0.0411</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0052 $\pm$ 0.0002</t>
+          <t>0.1195 $\pm$ 0.0330</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0387 $\pm$ 0.0081</t>
+          <t>0.1709 $\pm$ 0.0175</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0350 $\pm$ 0.0177</t>
+          <t>0.2381 $\pm$ 0.0657</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0349 $\pm$ 0.0144</t>
+          <t>0.1735 $\pm$ 0.0184</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0352 $\pm$ 0.0105</t>
+          <t>0.1712 $\pm$ 0.0175</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.3812 $\pm$ 0.0908</t>
+          <t>0.2187 $\pm$ 0.0845</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.2561 $\pm$ 0.1878</t>
+          <t>0.2507 $\pm$ 0.0855</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.2067 $\pm$ 0.1416</t>
+          <t>0.1752 $\pm$ 0.0210</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.1671 $\pm$ 0.1010</t>
+          <t>0.1837 $\pm$ 0.0304</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0183 $\pm$ 0.0065</t>
+          <t>4.9534 $\pm$ 1.7527</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1078 $\pm$ 0.0751</t>
+          <t>4.6212 $\pm$ 3.7207</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0811 $\pm$ 0.0544</t>
+          <t>4.8794 $\pm$ 2.2124</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0616 $\pm$ 0.0288</t>
+          <t>5.1890 $\pm$ 1.9521</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0394 $\pm$ 0.0222</t>
+          <t>0.6953 $\pm$ 0.3471</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1041 $\pm$ 0.0500</t>
+          <t>2.2459 $\pm$ 0.5407</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0930 $\pm$ 0.0429</t>
+          <t>0.7338 $\pm$ 0.3784</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0739 $\pm$ 0.0338</t>
+          <t>0.7254 $\pm$ 0.3588</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.9534 $\pm$ 1.7527</t>
+          <t>4.4387 $\pm$ 2.4365</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.6212 $\pm$ 3.7207</t>
+          <t>4.1360 $\pm$ 3.0144</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.8794 $\pm$ 2.2124</t>
+          <t>3.3390 $\pm$ 1.5476</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.1890 $\pm$ 1.9521</t>
+          <t>4.0282 $\pm$ 2.1750</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.6953 $\pm$ 0.3471</t>
+          <t>0.3280 $\pm$ 0.1003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.2459 $\pm$ 0.5407</t>
+          <t>0.9663 $\pm$ 0.1773</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.7338 $\pm$ 0.3784</t>
+          <t>0.4428 $\pm$ 0.0860</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.7254 $\pm$ 0.3588</t>
+          <t>0.3926 $\pm$ 0.0871</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.4387 $\pm$ 2.4365</t>
+          <t>3.9956 $\pm$ 2.1163</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.1360 $\pm$ 3.0144</t>
+          <t>4.3717 $\pm$ 3.4092</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.3390 $\pm$ 1.5476</t>
+          <t>3.6357 $\pm$ 2.0388</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.0282 $\pm$ 2.1750</t>
+          <t>3.8324 $\pm$ 2.1366</t>
         </is>
       </c>
     </row>

--- a/multi_regression/figs_100/regression_result.xlsx
+++ b/multi_regression/figs_100/regression_result.xlsx
@@ -1,43 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\phd\05_multiplayer_performative_stable\multiplayer-performative-stable\multi_regression\figs_100\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB99BC5-9DBA-498E-9B2B-45A4E2D96743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>$\sigma_A$ = 10.0</t>
+  </si>
+  <si>
+    <t>$\sigma_A$ = 2.5</t>
+  </si>
+  <si>
+    <t>$\sigma_A$ = 5.0</t>
+  </si>
+  <si>
+    <t>$\sigma_A$ = 7.5</t>
+  </si>
+  <si>
+    <t>SIR$^2$</t>
+  </si>
+  <si>
+    <t>0.0272 $\pm$ 0.0021</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>0.1229 $\pm$ 0.0370</t>
+  </si>
+  <si>
+    <t>0.1022 $\pm$ 0.0713</t>
+  </si>
+  <si>
+    <t>0.1145 $\pm$ 0.0411</t>
+  </si>
+  <si>
+    <t>0.1195 $\pm$ 0.0330</t>
+  </si>
+  <si>
+    <t>RGD</t>
+  </si>
+  <si>
+    <t>0.1709 $\pm$ 0.0175</t>
+  </si>
+  <si>
+    <t>0.2381 $\pm$ 0.0657</t>
+  </si>
+  <si>
+    <t>0.1735 $\pm$ 0.0184</t>
+  </si>
+  <si>
+    <t>0.1712 $\pm$ 0.0175</t>
+  </si>
+  <si>
+    <t>SFB</t>
+  </si>
+  <si>
+    <t>0.2187 $\pm$ 0.0845</t>
+  </si>
+  <si>
+    <t>0.2507 $\pm$ 0.0855</t>
+  </si>
+  <si>
+    <t>0.1752 $\pm$ 0.0210</t>
+  </si>
+  <si>
+    <t>0.1837 $\pm$ 0.0304</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>3.9956 $\pm$ 2.1163</t>
+  </si>
+  <si>
+    <t>4.3717 $\pm$ 3.4092</t>
+  </si>
+  <si>
+    <t>3.6357 $\pm$ 2.0388</t>
+  </si>
+  <si>
+    <t>3.8324 $\pm$ 2.1366</t>
+  </si>
+  <si>
+    <t>OPGD</t>
+  </si>
+  <si>
+    <t>0.3280 $\pm$ 0.1003</t>
+  </si>
+  <si>
+    <t>0.9663 $\pm$ 0.1773</t>
+  </si>
+  <si>
+    <t>0.4428 $\pm$ 0.0860</t>
+  </si>
+  <si>
+    <t>0.3926 $\pm$ 0.0871</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -46,93 +170,117 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,204 +568,288 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>$\sigma_A$ = 10.0</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>$\sigma_A$ = 2.5</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>$\sigma_A$ = 5.0</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>$\sigma_A$ = 7.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>SIR$^2$</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.0272 $\pm$ 0.0021</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.0272 $\pm$ 0.0021</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.0272 $\pm$ 0.0021</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0272 $\pm$ 0.0021</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.1229 $\pm$ 0.0370</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.1022 $\pm$ 0.0713</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.1145 $\pm$ 0.0411</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.1195 $\pm$ 0.0330</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>RGD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.1709 $\pm$ 0.0175</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.2381 $\pm$ 0.0657</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.1735 $\pm$ 0.0184</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.1712 $\pm$ 0.0175</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SFB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.2187 $\pm$ 0.0845</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.2507 $\pm$ 0.0855</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.1752 $\pm$ 0.0210</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.1837 $\pm$ 0.0304</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3.9956 $\pm$ 2.1163</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.3717 $\pm$ 3.4092</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.6357 $\pm$ 2.0388</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3.8324 $\pm$ 2.1366</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OPGD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.3280 $\pm$ 0.1003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.9663 $\pm$ 0.1773</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.4428 $\pm$ 0.0860</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.3926 $\pm$ 0.0871</t>
-        </is>
-      </c>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K10" s="6"/>
+      <c r="L10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="11:16" x14ac:dyDescent="0.25">
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="11:16" x14ac:dyDescent="0.25">
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="11:16" x14ac:dyDescent="0.25">
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="11:16" x14ac:dyDescent="0.25">
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>